--- a/data/trans_orig/P1426-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1426-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2012</t>
+          <t>Población con diagnóstico de hipoacusia en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21364</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283646</t>
+          <t>283252</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292842</t>
+          <t>292891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271541</t>
+          <t>272290</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284600</t>
+          <t>284482</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560619</t>
+          <t>561999</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575941</t>
+          <t>575816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25839</t>
+          <t>24348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9711</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28325</t>
+          <t>28440</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490423</t>
+          <t>492685</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497926</t>
+          <t>499417</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516283</t>
+          <t>516075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1000967</t>
+          <t>1000852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019581</t>
+          <t>1020606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20151</t>
+          <t>20644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309883</t>
+          <t>310708</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322678</t>
+          <t>322664</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329325</t>
+          <t>329601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>339007</t>
+          <t>339045</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644915</t>
+          <t>644422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>659958</t>
+          <t>659934</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15015</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>365074</t>
+          <t>365760</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373015</t>
+          <t>373017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>378093</t>
+          <t>376983</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387052</t>
+          <t>386995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>747918</t>
+          <t>746707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>759651</t>
+          <t>758876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>15092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21630</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30888</t>
+          <t>29518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196490</t>
+          <t>197526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209330</t>
+          <t>209564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197961</t>
+          <t>198285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213449</t>
+          <t>213358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>401321</t>
+          <t>402691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>419813</t>
+          <t>420542</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258401</t>
+          <t>258464</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269976</t>
+          <t>270148</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267076</t>
+          <t>268486</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277010</t>
+          <t>277093</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>530981</t>
+          <t>532026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>545729</t>
+          <t>545811</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27080</t>
+          <t>28160</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39602</t>
+          <t>40968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>635708</t>
+          <t>634628</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>653571</t>
+          <t>653684</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>674883</t>
+          <t>675073</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688667</t>
+          <t>688517</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1317039</t>
+          <t>1315673</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1339692</t>
+          <t>1339252</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14517</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22142</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>768160</t>
+          <t>767568</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777965</t>
+          <t>777986</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>808061</t>
+          <t>807589</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819381</t>
+          <t>819231</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1579534</t>
+          <t>1580874</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1595164</t>
+          <t>1595197</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39092</t>
+          <t>38818</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69570</t>
+          <t>69833</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>49811</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>83920</t>
+          <t>83422</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>97841</t>
+          <t>98274</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>142573</t>
+          <t>144032</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3357209</t>
+          <t>3356946</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3387687</t>
+          <t>3387961</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3471178</t>
+          <t>3471676</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3505287</t>
+          <t>3504696</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6839304</t>
+          <t>6837845</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6884036</t>
+          <t>6883603</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2016</t>
+          <t>Población con diagnóstico de hipoacusia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14196</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>15795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25176</t>
+          <t>25626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279565</t>
+          <t>279005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290715</t>
+          <t>290919</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274633</t>
+          <t>272908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284823</t>
+          <t>284890</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>557288</t>
+          <t>556838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>573769</t>
+          <t>573298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15926</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495623</t>
+          <t>494984</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501834</t>
+          <t>501837</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509668</t>
+          <t>510206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520839</t>
+          <t>520847</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009733</t>
+          <t>1009578</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022208</t>
+          <t>1021851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312351</t>
+          <t>312629</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328165</t>
+          <t>327094</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335410</t>
+          <t>335407</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643916</t>
+          <t>643561</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653059</t>
+          <t>653174</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14340</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10922</t>
+          <t>11052</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>20467</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>355624</t>
+          <t>354619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366879</t>
+          <t>367166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376361</t>
+          <t>376231</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>737000</t>
+          <t>736780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752331</t>
+          <t>752399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20630</t>
+          <t>19733</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202069</t>
+          <t>200399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202139</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214620</t>
+          <t>214342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>409178</t>
+          <t>410075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>423575</t>
+          <t>424325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10827</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252296</t>
+          <t>251670</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261976</t>
+          <t>261105</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258148</t>
+          <t>257258</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269289</t>
+          <t>269047</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>513789</t>
+          <t>514660</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>528613</t>
+          <t>529139</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21445</t>
+          <t>22114</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19843</t>
+          <t>21075</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44016</t>
+          <t>42975</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31412</t>
+          <t>32127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57501</t>
+          <t>60484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>635113</t>
+          <t>634444</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648976</t>
+          <t>648901</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>647278</t>
+          <t>648319</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>671451</t>
+          <t>670219</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1290351</t>
+          <t>1287368</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1316440</t>
+          <t>1315725</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>16369</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24071</t>
+          <t>24451</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>761142</t>
+          <t>762214</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773722</t>
+          <t>774060</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>814235</t>
+          <t>814120</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>824079</t>
+          <t>824097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1580679</t>
+          <t>1580299</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1596388</t>
+          <t>1596535</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36995</t>
+          <t>36588</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65415</t>
+          <t>65709</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55721</t>
+          <t>57185</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>90268</t>
+          <t>91946</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>100457</t>
+          <t>99982</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>145200</t>
+          <t>145331</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3328935</t>
+          <t>3328641</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3357355</t>
+          <t>3357762</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3454274</t>
+          <t>3452596</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3488821</t>
+          <t>3487357</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6793692</t>
+          <t>6793561</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6838435</t>
+          <t>6838910</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2023</t>
+          <t>Población con diagnóstico de hipoacusia en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18338</t>
+          <t>17966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>299456</t>
+          <t>300539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308981</t>
+          <t>309318</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279757</t>
+          <t>279213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286670</t>
+          <t>286383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582739</t>
+          <t>583111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>594054</t>
+          <t>594108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20801</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31510</t>
+          <t>30938</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496592</t>
+          <t>497090</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511357</t>
+          <t>511474</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498124</t>
+          <t>497587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508342</t>
+          <t>507854</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>999574</t>
+          <t>1000146</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1017282</t>
+          <t>1017426</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21513</t>
+          <t>21761</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39758</t>
+          <t>38911</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15351</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28705</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39952</t>
+          <t>40002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62266</t>
+          <t>62217</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276292</t>
+          <t>277139</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>294537</t>
+          <t>294289</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>320423</t>
+          <t>321439</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333777</t>
+          <t>334414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602912</t>
+          <t>602961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>625226</t>
+          <t>625176</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,47 +8422,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>15544</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8729</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22637</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15544</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8645</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>22617</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34782</t>
+          <t>34614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296044</t>
+          <t>295932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>306842</t>
+          <t>306986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,49 +8535,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>460174</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>453081</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>466989</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,24%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>98,17%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>460174</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>453101</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>467073</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>842</t>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>753492</t>
+          <t>753660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>771332</t>
+          <t>771229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>12278</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21727</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23896</t>
+          <t>23537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38048</t>
+          <t>37579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159663</t>
+          <t>158993</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170091</t>
+          <t>169692</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>185755</t>
+          <t>185673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195210</t>
+          <t>195204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>348176</t>
+          <t>348645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>362328</t>
+          <t>362687</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28614</t>
+          <t>28514</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45434</t>
+          <t>45410</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>24897</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39058</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58089</t>
+          <t>57756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79857</t>
+          <t>79565</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224202</t>
+          <t>224226</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241022</t>
+          <t>241122</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>217329</t>
+          <t>217948</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>231104</t>
+          <t>231490</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>446166</t>
+          <t>446458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>467934</t>
+          <t>468267</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45387</t>
+          <t>45946</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21147</t>
+          <t>20433</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63976</t>
+          <t>62951</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48056</t>
+          <t>49306</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97608</t>
+          <t>98121</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>577002</t>
+          <t>576443</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597776</t>
+          <t>598465</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>784497</t>
+          <t>785522</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>827326</t>
+          <t>828040</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1373254</t>
+          <t>1372741</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1422806</t>
+          <t>1421556</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>11588</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24734</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41856</t>
+          <t>42696</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>905849</t>
+          <t>905075</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>923201</t>
+          <t>923060</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>690658</t>
+          <t>691145</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>703537</t>
+          <t>703804</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1602256</t>
+          <t>1601416</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1626130</t>
+          <t>1625403</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>120677</t>
+          <t>118802</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>179778</t>
+          <t>179133</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>132119</t>
+          <t>130509</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>182663</t>
+          <t>181385</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>273975</t>
+          <t>272030</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>350189</t>
+          <t>351359</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3277152</t>
+          <t>3277797</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3336253</t>
+          <t>3338128</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3473241</t>
+          <t>3474519</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3523785</t>
+          <t>3525395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6762645</t>
+          <t>6761475</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6838859</t>
+          <t>6840804</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1426-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1426-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>10969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283252</t>
+          <t>283769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292891</t>
+          <t>292886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272290</t>
+          <t>272899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284482</t>
+          <t>284276</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561999</t>
+          <t>560851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575816</t>
+          <t>575558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>11893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24348</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28440</t>
+          <t>28459</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492685</t>
+          <t>493634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499417</t>
+          <t>498755</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516075</t>
+          <t>515915</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1000852</t>
+          <t>1000833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1020606</t>
+          <t>1019735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>13915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>11362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20644</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310708</t>
+          <t>310131</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322664</t>
+          <t>322659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329601</t>
+          <t>329658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>339045</t>
+          <t>339018</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644422</t>
+          <t>646205</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>659934</t>
+          <t>660083</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11968</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>365760</t>
+          <t>365861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373017</t>
+          <t>373015</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376983</t>
+          <t>377854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386995</t>
+          <t>387056</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>746707</t>
+          <t>747326</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>758876</t>
+          <t>759079</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>20991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29518</t>
+          <t>31144</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197526</t>
+          <t>197556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209564</t>
+          <t>209374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198285</t>
+          <t>198600</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213358</t>
+          <t>213327</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>402691</t>
+          <t>401065</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>420542</t>
+          <t>420089</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258464</t>
+          <t>258657</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270148</t>
+          <t>270748</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>268486</t>
+          <t>268429</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277093</t>
+          <t>277003</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>532026</t>
+          <t>529750</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>545811</t>
+          <t>544727</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28160</t>
+          <t>27283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40968</t>
+          <t>39627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>634628</t>
+          <t>635505</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>653684</t>
+          <t>653629</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>675073</t>
+          <t>674948</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688517</t>
+          <t>688586</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1315673</t>
+          <t>1317014</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1339252</t>
+          <t>1339439</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14989</t>
+          <t>14726</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20802</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>767568</t>
+          <t>768414</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777986</t>
+          <t>777993</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>807589</t>
+          <t>807852</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819231</t>
+          <t>819275</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1580874</t>
+          <t>1580406</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1595197</t>
+          <t>1596109</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38818</t>
+          <t>38013</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69833</t>
+          <t>68462</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>50236</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>83422</t>
+          <t>83816</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>98274</t>
+          <t>98281</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>144032</t>
+          <t>147293</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3356946</t>
+          <t>3358317</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3387961</t>
+          <t>3388766</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3471676</t>
+          <t>3471282</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3504696</t>
+          <t>3504862</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6837845</t>
+          <t>6834584</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6883603</t>
+          <t>6883596</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>14208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25626</t>
+          <t>24289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279005</t>
+          <t>279553</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290919</t>
+          <t>290619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272908</t>
+          <t>273126</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284890</t>
+          <t>284910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>556838</t>
+          <t>558175</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>573298</t>
+          <t>573700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>15949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494984</t>
+          <t>494676</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501837</t>
+          <t>501834</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510206</t>
+          <t>510504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520847</t>
+          <t>520902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009578</t>
+          <t>1009710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021851</t>
+          <t>1021856</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>886</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312629</t>
+          <t>312916</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327094</t>
+          <t>328052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335407</t>
+          <t>335423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643561</t>
+          <t>642534</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653174</t>
+          <t>653035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15345</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20467</t>
+          <t>20092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>354619</t>
+          <t>355158</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367166</t>
+          <t>366928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376231</t>
+          <t>376346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>736780</t>
+          <t>737155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752399</t>
+          <t>752532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>16508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19733</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200399</t>
+          <t>201787</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202079</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214342</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410075</t>
+          <t>408683</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424325</t>
+          <t>423821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11453</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251670</t>
+          <t>251655</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261105</t>
+          <t>261551</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>257258</t>
+          <t>257096</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269047</t>
+          <t>269247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514660</t>
+          <t>514803</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>529139</t>
+          <t>529410</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21075</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42975</t>
+          <t>42832</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32127</t>
+          <t>31002</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60484</t>
+          <t>57523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>634444</t>
+          <t>634349</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648901</t>
+          <t>648868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>648319</t>
+          <t>648462</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>670219</t>
+          <t>671921</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1287368</t>
+          <t>1290329</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1315725</t>
+          <t>1316850</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24451</t>
+          <t>23799</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762214</t>
+          <t>761677</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774060</t>
+          <t>773885</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>814120</t>
+          <t>813448</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>824097</t>
+          <t>824072</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1580299</t>
+          <t>1580951</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1596535</t>
+          <t>1596776</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36588</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65709</t>
+          <t>64386</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>57185</t>
+          <t>55309</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>91946</t>
+          <t>91540</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>99982</t>
+          <t>100489</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>145331</t>
+          <t>148343</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3328641</t>
+          <t>3329964</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3357762</t>
+          <t>3358014</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3452596</t>
+          <t>3453002</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3487357</t>
+          <t>3489233</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6793561</t>
+          <t>6790549</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6838910</t>
+          <t>6838403</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -7373,32 +7373,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>11769</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>10934</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,27 +7443,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17966</t>
+          <t>18999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -7486,32 +7486,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>305705</t>
+          <t>312717</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300539</t>
+          <t>307076</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309318</t>
+          <t>315940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7521,32 +7521,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>283818</t>
+          <t>309836</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279213</t>
+          <t>305127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286383</t>
+          <t>312645</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7556,22 +7556,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>589522</t>
+          <t>622553</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>583111</t>
+          <t>615907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>594108</t>
+          <t>627139</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20303</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>22192</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>33547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505901</t>
+          <t>517738</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>497090</t>
+          <t>508542</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511474</t>
+          <t>523441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>503870</t>
+          <t>534924</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497587</t>
+          <t>528527</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507854</t>
+          <t>539666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1009772</t>
+          <t>1052662</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1000146</t>
+          <t>1041307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1017426</t>
+          <t>1059761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513691</t>
+          <t>545194</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513691</t>
+          <t>545194</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513691</t>
+          <t>545194</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031084</t>
+          <t>1074854</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031084</t>
+          <t>1074854</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031084</t>
+          <t>1074854</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29645</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21761</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38911</t>
+          <t>38846</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>27423</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49859</t>
+          <t>49271</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40002</t>
+          <t>39688</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62217</t>
+          <t>61221</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>286405</t>
+          <t>286945</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277139</t>
+          <t>277147</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>294289</t>
+          <t>295401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>328914</t>
+          <t>336158</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321439</t>
+          <t>328958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334414</t>
+          <t>342092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>615319</t>
+          <t>623104</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602961</t>
+          <t>611154</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>625176</t>
+          <t>632687</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5885</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>18381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>17017</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22637</t>
+          <t>23087</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,32 +8472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>25459</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>20848</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34614</t>
+          <t>37341</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>302641</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>295932</t>
+          <t>354764</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>306986</t>
+          <t>367260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,32 +8550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>460174</t>
+          <t>404944</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>453081</t>
+          <t>398874</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466989</t>
+          <t>409960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>762815</t>
+          <t>767457</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>753660</t>
+          <t>757766</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>771229</t>
+          <t>774259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,32 +8745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13426</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>20938</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16491</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12278</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>23080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>29916</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23537</t>
+          <t>25318</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37579</t>
+          <t>40098</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -8858,32 +8858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>165316</t>
+          <t>191106</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158993</t>
+          <t>184727</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169692</t>
+          <t>196074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>190991</t>
+          <t>208362</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>185673</t>
+          <t>202905</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195204</t>
+          <t>213240</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>356308</t>
+          <t>399467</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>348645</t>
+          <t>391551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>362687</t>
+          <t>406331</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207482</t>
+          <t>225985</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207482</t>
+          <t>225985</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207482</t>
+          <t>225985</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386224</t>
+          <t>431649</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386224</t>
+          <t>431649</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386224</t>
+          <t>431649</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,32 +9088,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36257</t>
+          <t>36645</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>28839</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45410</t>
+          <t>45565</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,32 +9123,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31437</t>
+          <t>32086</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>25690</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>41095</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>67695</t>
+          <t>68731</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57756</t>
+          <t>58066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79565</t>
+          <t>80250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -9201,32 +9201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>233379</t>
+          <t>234062</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224226</t>
+          <t>225142</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241122</t>
+          <t>241868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9236,32 +9236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>224950</t>
+          <t>231013</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>217948</t>
+          <t>222004</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>231490</t>
+          <t>237409</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>458328</t>
+          <t>465075</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>446458</t>
+          <t>453556</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>468267</t>
+          <t>475740</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33612</t>
+          <t>39683</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23924</t>
+          <t>28032</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>53916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>43775</t>
+          <t>51415</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20433</t>
+          <t>40855</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62951</t>
+          <t>64980</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>77387</t>
+          <t>91098</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49306</t>
+          <t>75295</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98121</t>
+          <t>110321</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>588777</t>
+          <t>677968</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>576443</t>
+          <t>663735</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598465</t>
+          <t>689619</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,32 +9579,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>804698</t>
+          <t>719275</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>785522</t>
+          <t>705710</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>828040</t>
+          <t>729835</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1393475</t>
+          <t>1397243</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1372741</t>
+          <t>1378020</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1421556</t>
+          <t>1413046</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>622389</t>
+          <t>717651</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>622389</t>
+          <t>717651</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622389</t>
+          <t>717651</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848473</t>
+          <t>770690</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848473</t>
+          <t>770690</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848473</t>
+          <t>770690</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1470862</t>
+          <t>1488341</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1470862</t>
+          <t>1488341</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1470862</t>
+          <t>1488341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>15491</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23645</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>27769</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9844,32 +9844,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>31353</t>
+          <t>35143</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>25694</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42696</t>
+          <t>45263</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -9887,32 +9887,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>914669</t>
+          <t>782581</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>905075</t>
+          <t>774131</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>923060</t>
+          <t>788584</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9922,32 +9922,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>698090</t>
+          <t>810957</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>691145</t>
+          <t>802840</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>703804</t>
+          <t>816887</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9957,32 +9957,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1612759</t>
+          <t>1593538</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1601416</t>
+          <t>1583418</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1625403</t>
+          <t>1602987</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>154136</t>
+          <t>164110</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>118802</t>
+          <t>143078</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>179133</t>
+          <t>185982</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>160400</t>
+          <t>174510</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>130509</t>
+          <t>154437</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>181385</t>
+          <t>193746</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>314536</t>
+          <t>338620</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>272030</t>
+          <t>307362</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>351359</t>
+          <t>366562</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3302794</t>
+          <t>3365628</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3277797</t>
+          <t>3343756</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3338128</t>
+          <t>3386660</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3495504</t>
+          <t>3555471</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3474519</t>
+          <t>3536235</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3525395</t>
+          <t>3575544</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6798298</t>
+          <t>6921099</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6761475</t>
+          <t>6893157</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6840804</t>
+          <t>6952357</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3456930</t>
+          <t>3529738</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3456930</t>
+          <t>3529738</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3456930</t>
+          <t>3529738</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3655904</t>
+          <t>3729981</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3655904</t>
+          <t>3729981</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3655904</t>
+          <t>3729981</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7112834</t>
+          <t>7259719</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7112834</t>
+          <t>7259719</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7112834</t>
+          <t>7259719</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
